--- a/public/assets/excel-template/e-PGS_STUDENT_REGISTRATION_TEMPLATE.xlsx
+++ b/public/assets/excel-template/e-PGS_STUDENT_REGISTRATION_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\fyp-project\public\assets\excel-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E2629D-BDA9-4EA9-B283-573E6E654F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00C2962-9226-4C29-A31A-0747CE89EC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7205C628-2ECF-4FA1-95A4-550522F5FFD8}"/>
+    <workbookView xWindow="18645" yWindow="885" windowWidth="17280" windowHeight="8880" xr2:uid="{7205C628-2ECF-4FA1-95A4-550522F5FFD8}"/>
   </bookViews>
   <sheets>
     <sheet name="e-PGS Student Registration" sheetId="1" r:id="rId1"/>
@@ -75,9 +75,6 @@
     <t>EX. MUHAMMAD ZIKRI BIN KASHIM</t>
   </si>
   <si>
-    <t>EX. M / F</t>
-  </si>
-  <si>
     <t>EX. b032320098@student.utem.edu.my</t>
   </si>
   <si>
@@ -87,12 +84,6 @@
     <t>EX. No 43, Jalan Beriksa 5, Taman Akasia, 75350</t>
   </si>
   <si>
-    <t>EX. PITA / MITA</t>
-  </si>
-  <si>
-    <t>EX. PT / FT</t>
-  </si>
-  <si>
     <t>EX . A0234</t>
   </si>
   <si>
@@ -100,6 +91,15 @@
   </si>
   <si>
     <t>EX. Research 1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>MITA</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
 </sst>
 </file>
@@ -276,47 +276,48 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -335,7 +336,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -435,11 +435,11 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{002C293F-6CD3-43DB-8B76-2B45D8CD0133}" name="matricno" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{DB84A27A-0797-4B18-9545-949A00AC4C8F}" name="student_name" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{5BE1E198-3C68-4579-9137-AFA55E17354A}" name="gender" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5BE1E198-3C68-4579-9137-AFA55E17354A}" name="gender" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{A216302B-9EF0-4830-97A8-6B0FF133C2A2}" name="email" dataCellStyle="Hyperlink"/>
-    <tableColumn id="4" xr3:uid="{66572F2B-D61C-4A5D-B912-65213296A877}" name="phoneno" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{8D7FC06C-E2FB-4648-86A0-142CE8C5F69A}" name="address" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{E8F7AD5E-D903-4183-B7D5-35BEC0A95353}" name="programme_code" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{66572F2B-D61C-4A5D-B912-65213296A877}" name="phoneno" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{8D7FC06C-E2FB-4648-86A0-142CE8C5F69A}" name="address" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{E8F7AD5E-D903-4183-B7D5-35BEC0A95353}" name="programme_code" dataDxfId="4"/>
     <tableColumn id="8" xr3:uid="{529B9316-9426-4296-BE74-32309620269E}" name="programme_mode" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{5D8CF052-BBA8-4B7A-9A83-E924FE5E5485}" name="main_supervisor_id" dataDxfId="2"/>
     <tableColumn id="10" xr3:uid="{35B78A0D-E964-4667-A682-A755EA712A44}" name="co_supervisor_id" dataDxfId="1"/>
@@ -747,23 +747,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40EAC937-8C1A-415E-B4D3-7BDDC8094CE5}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="41.88671875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="43.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="43.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" style="1" customWidth="1"/>
     <col min="11" max="11" width="27" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="12" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -798,7 +798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -806,35 +806,46 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{C13BBF83-A0DF-42D0-99E5-D6D338A69A04}">
+      <formula1>"M, F"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{08BFBC62-FDCA-4F9F-8B5B-079579A1C4C5}">
+      <formula1>"PITA,MITA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{73B1D130-C729-4A15-923C-B567ED464AA5}">
+      <formula1>"PT,FT"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="b032320098@student.utem.edu.my" xr:uid="{09BD03F4-E134-4C57-BA13-729CEF0C2C42}"/>
   </hyperlinks>
